--- a/data/output/2025/evaluasi_65.xlsx
+++ b/data/output/2025/evaluasi_65.xlsx
@@ -924,7 +924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1068,6 +1068,146 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6501</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Malinau</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-3.880776536652566</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6501</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Malinau</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>18.25000000000001</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6501</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Malinau</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6501</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Malinau</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6.092411845627963</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6501</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Malinau</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.222632244630659</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1226,6 +1366,230 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6503</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Tidung</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-5.259887599190771</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6503</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Tidung</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2751650008055646</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6503</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Tidung</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.16095624741798</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6503</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Tidung</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6503</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Tidung</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5.873399595046997</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6503</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Tidung</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3.52492635872725</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6503</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Tidung</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.8937750194998491</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6503</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Tidung</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.7622882010885337</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1356,6 +1720,230 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6502</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bulungan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-24.37374528557642</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6502</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bulungan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.782034770387719</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6502</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Bulungan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>21.57923845389034</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6502</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Bulungan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6502</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Bulungan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2.603427244930554</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6502</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Bulungan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.207446987657373</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6502</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Bulungan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.387678571421367</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6502</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Bulungan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.03921361313436452</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1486,6 +2074,174 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6571</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Tarakan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-4.818751930953318</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6571</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Tarakan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12.62879140945923</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6571</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Tarakan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6571</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Tarakan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3.03875600537445</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6571</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Tarakan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.9766248866072283</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6571</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Tarakan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.1539691037628511</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1500,7 +2256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1563,6 +2319,146 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6504</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Nunukan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>19.5157715373874</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6504</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Nunukan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6504</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Nunukan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2.861294705815984</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6504</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Nunukan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.361036217647669</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6504</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Nunukan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.399111693641373</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
